--- a/tools/Machiavelli Roguelike.xlsx
+++ b/tools/Machiavelli Roguelike.xlsx
@@ -5,15 +5,15 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Owner\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Owner\Documents\Machiavelli Roguelike\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBF39515-DDE9-4AAD-9E5E-D790DE4DAA65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEC99D93-60E9-4CA1-950F-F68EA4B06B84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Locations" sheetId="1" r:id="rId1"/>
+    <sheet name="Instances" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,14 +25,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="32">
   <si>
     <t>Cycle</t>
   </si>
   <si>
-    <t>On reveal</t>
-  </si>
-  <si>
     <t>Choose 2 cards to discard, then draw 2</t>
   </si>
   <si>
@@ -88,6 +85,42 @@
   </si>
   <si>
     <t>+2 max energy</t>
+  </si>
+  <si>
+    <t>Wild Card</t>
+  </si>
+  <si>
+    <t>Reveal</t>
+  </si>
+  <si>
+    <t>Draw 1 of your Jokers</t>
+  </si>
+  <si>
+    <t>Give 2 random cards random suits and ranks</t>
+  </si>
+  <si>
+    <t>Jumble</t>
+  </si>
+  <si>
+    <t>Effect</t>
+  </si>
+  <si>
+    <t>Jackpot</t>
+  </si>
+  <si>
+    <t>7s cost 0 Energy</t>
+  </si>
+  <si>
+    <t>Give 2 random cards -1 Energy Cost and 2 other random cards +2 Energy Cost</t>
+  </si>
+  <si>
+    <t>Syphon</t>
+  </si>
+  <si>
+    <t>Black Hole</t>
+  </si>
+  <si>
+    <t>Destroy a random Combo on the board</t>
   </si>
 </sst>
 </file>
@@ -148,12 +181,13 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{11F6E3B6-0BAE-4938-9A0B-E725E92BD65A}" name="Table1" displayName="Table1" ref="A1:C9" totalsRowShown="0">
-  <autoFilter ref="A1:C9" xr:uid="{11F6E3B6-0BAE-4938-9A0B-E725E92BD65A}"/>
-  <tableColumns count="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{11F6E3B6-0BAE-4938-9A0B-E725E92BD65A}" name="Table1" displayName="Table1" ref="A1:D14" totalsRowShown="0">
+  <autoFilter ref="A1:D14" xr:uid="{11F6E3B6-0BAE-4938-9A0B-E725E92BD65A}"/>
+  <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{BC82BB34-C313-4BF0-A704-4B00A7DEF4FD}" name="Name"/>
     <tableColumn id="2" xr3:uid="{E4EDBCBD-30DD-46F3-AEAE-2B73220CE546}" name="Type"/>
     <tableColumn id="3" xr3:uid="{7328CD1E-B286-4127-8204-5634E69D2CF5}" name="Description" dataDxfId="0"/>
+    <tableColumn id="4" xr3:uid="{028AAE2E-6418-4CE6-B017-0A03A6350457}" name="Effect"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -422,111 +456,170 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="69.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" t="s">
         <v>17</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="1" t="s">
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="B3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="1" t="s">
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="1" t="s">
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="B5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C5" s="1" t="s">
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="B6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" t="s">
         <v>9</v>
       </c>
-      <c r="B6" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" s="1" t="s">
+      <c r="C7" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>16</v>
+      <c r="B10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/tools/Machiavelli Roguelike.xlsx
+++ b/tools/Machiavelli Roguelike.xlsx
@@ -462,7 +462,7 @@
     <col min="1" max="1" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="40.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -489,6 +489,11 @@
       <c r="C2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>discard choose 2; draw 2</t>
+        </is>
+      </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
@@ -500,6 +505,11 @@
       <c r="C3" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>give choose 2</t>
+        </is>
+      </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
@@ -511,6 +521,11 @@
       <c r="C4" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>energy +3</t>
+        </is>
+      </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
@@ -522,6 +537,11 @@
       <c r="C5" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>coins_per_card 1</t>
+        </is>
+      </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
@@ -533,6 +553,11 @@
       <c r="C6" s="1" t="s">
         <v>19</v>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>max_energy +2</t>
+        </is>
+      </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
@@ -544,6 +569,11 @@
       <c r="C7" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>draw_bonus 1</t>
+        </is>
+      </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
@@ -555,6 +585,11 @@
       <c r="C8" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>discard random 1</t>
+        </is>
+      </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
@@ -566,6 +601,11 @@
       <c r="C9" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>open_decks</t>
+        </is>
+      </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
@@ -577,6 +617,11 @@
       <c r="C10" s="1" t="s">
         <v>22</v>
       </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>draw_joker 1</t>
+        </is>
+      </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
@@ -588,6 +633,11 @@
       <c r="C11" s="1" t="s">
         <v>23</v>
       </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>jumble random 2</t>
+        </is>
+      </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
@@ -599,6 +649,11 @@
       <c r="C12" s="1" t="s">
         <v>27</v>
       </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>cost rank=7 0</t>
+        </is>
+      </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
@@ -610,6 +665,11 @@
       <c r="C13" s="1" t="s">
         <v>28</v>
       </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>cost random 2 -1; cost random 2 +2</t>
+        </is>
+      </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
@@ -620,6 +680,11 @@
       </c>
       <c r="C14" s="1" t="s">
         <v>31</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>destroy combo random</t>
+        </is>
       </c>
     </row>
   </sheetData>
